--- a/assets/starter-pack/rebuilt/FLK_05_WOSB_EDWOSB_Self_Cert.xlsx
+++ b/assets/starter-pack/rebuilt/FLK_05_WOSB_EDWOSB_Self_Cert.xlsx
@@ -4,20 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Business Profile" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="WOSB Eligibility" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="EDWOSB Net Worth" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Document Checklist" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Eligible NAICS" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Summary" state="visible" r:id="rId10"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Business Profile" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="WOSB Eligibility" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="EDWOSB Net Worth" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Document Checklist" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Eligible NAICS" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Summary" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="CitizenStatus">Lists!$A$2:$A$5,'Business Profile'!$C$18</definedName>
+    <definedName name="YesNoMaybe">Lists!$B$2:$B$4</definedName>
+    <definedName name="DocStatus">Lists!$C$2:$C$4,'Document Checklist'!$F$5:$F$32</definedName>
     <definedName name="BusinessName">'Business Profile'!$C$4</definedName>
     <definedName name="PrimaryNAICS">'Business Profile'!$C$8</definedName>
     <definedName name="AvgRevenue">'Business Profile'!$C$13</definedName>
     <definedName name="FemaleOwnerPct">'Business Profile'!$C$17</definedName>
-    <definedName name="CitizenStatus">'Business Profile'!$C$18</definedName>
     <definedName name="CombinedFemalePct">'Business Profile'!$C$22</definedName>
     <definedName name="HighestMalePct">'Business Profile'!$C$23</definedName>
     <definedName name="WOSBCore">'WOSB Eligibility'!$D$5:$D$13</definedName>
@@ -25,13 +28,12 @@
     <definedName name="EDWOSBTests">'WOSB Eligibility'!$D$22:$D$26</definedName>
     <definedName name="WOSBDocs">'WOSB Eligibility'!$D$28:$D$31</definedName>
     <definedName name="WOSBAll">'WOSB Eligibility'!$D$5:$D$31</definedName>
-    <definedName name="DocStatus">'Document Checklist'!$F$5:$F$32</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -119,7 +121,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="319">
+  <si>
+    <t>Citizen Status</t>
+  </si>
+  <si>
+    <t>Y / N / ?</t>
+  </si>
+  <si>
+    <t>Document Status</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Have</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Need</t>
+  </si>
+  <si>
+    <t>Naturalized</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Dual citizen</t>
+  </si>
   <si>
     <t>WOSB / EDWOSB Self-Certification Pack</t>
   </si>
@@ -1047,12 +1088,21 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1163,12 +1213,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF065F46"/>
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FF065F46"/>
       </patternFill>
     </fill>
     <fill>
@@ -1259,136 +1309,142 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1928,6 +1984,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1939,193 +2058,193 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>3</v>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>4</v>
+      <c r="B5" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>5</v>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>6</v>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>7</v>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>8</v>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>9</v>
+      <c r="B12" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>10</v>
+      <c r="B13" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>11</v>
+      <c r="B14" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>12</v>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>13</v>
+      <c r="B16" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>14</v>
+      <c r="B18" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>15</v>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>16</v>
+      <c r="B21" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>17</v>
+      <c r="B22" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>18</v>
+      <c r="B24" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="25" ht="80" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>19</v>
+      <c r="B25" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>20</v>
+      <c r="B27" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>21</v>
+      <c r="B28" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>22</v>
+      <c r="B29" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
-        <v>23</v>
+      <c r="B30" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>24</v>
+      <c r="B31" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
-        <v>25</v>
+      <c r="B32" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>26</v>
+      <c r="B34" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="35" ht="64" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
-        <v>27</v>
+      <c r="B35" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2142,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2159,257 +2278,257 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
+      <c r="B3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>34</v>
+      <c r="B4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>36</v>
+      <c r="B5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>38</v>
+      <c r="B6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>40</v>
+      <c r="B7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>42</v>
+      <c r="B8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>44</v>
+      <c r="B9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>46</v>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>48</v>
+      <c r="B11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>50</v>
+      <c r="B12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>52</v>
+      <c r="B13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>54</v>
+      <c r="B15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>56</v>
+      <c r="B16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>58</v>
+      <c r="B17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>61</v>
+      <c r="B18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>63</v>
+      <c r="B19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>65</v>
+      <c r="B21" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>67</v>
+      <c r="B22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>69</v>
+      <c r="B23" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>71</v>
+      <c r="B25" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>73</v>
+      <c r="B26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2419,7 +2538,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose one" error="Pick from the dropdown" sqref="C18">
-      <formula1>"Yes,No,Naturalized,Dual citizen"</formula1>
+      <formula1>CitizenStatus</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2431,7 +2550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2448,562 +2567,562 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>2</v>
+      <c r="C6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
+      <c r="B7" s="13">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>2</v>
+      <c r="C7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+      <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>2</v>
+      <c r="C8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+      <c r="B9" s="13">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>2</v>
+      <c r="C9" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
+      <c r="B10" s="13">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>2</v>
+      <c r="C10" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+      <c r="B11" s="13">
         <v>7</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>2</v>
+      <c r="C11" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="B12" s="13">
         <v>8</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>2</v>
+      <c r="C12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="11">
+      <c r="B13" s="13">
         <v>9</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>2</v>
+      <c r="C13" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="11">
+      <c r="B15" s="13">
         <v>10</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>2</v>
+      <c r="C15" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
+      <c r="B16" s="13">
         <v>11</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>2</v>
+      <c r="C16" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="11">
+      <c r="B17" s="13">
         <v>12</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>2</v>
+      <c r="F17" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="11">
+      <c r="B18" s="13">
         <v>13</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>2</v>
+      <c r="C18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="11">
+      <c r="B19" s="13">
         <v>14</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>2</v>
+      <c r="C19" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="11">
-        <v>15</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>2</v>
+      <c r="B20" s="13">
+        <v>15</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="B21" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
     </row>
     <row r="22" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="11">
+      <c r="B22" s="13">
         <v>16</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>2</v>
+      <c r="C22" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="11">
+      <c r="B23" s="13">
         <v>17</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>2</v>
+      <c r="C23" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="11">
+      <c r="B24" s="13">
         <v>18</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>2</v>
+      <c r="C24" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="11">
+      <c r="B25" s="13">
         <v>19</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>2</v>
+      <c r="C25" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="11">
+      <c r="B26" s="13">
         <v>20</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>2</v>
+      <c r="C26" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
+      <c r="B27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="11">
+      <c r="B28" s="13">
         <v>21</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>2</v>
+      <c r="C28" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="11">
+      <c r="B29" s="13">
         <v>22</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>2</v>
+      <c r="F29" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="11">
+      <c r="B30" s="13">
         <v>23</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>2</v>
+      <c r="C30" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <v>24</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>2</v>
+      <c r="C31" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="17" t="str">
+      <c r="B33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="19" t="str">
         <f>COUNTIF(D5:D13,"Y")&amp;" of 9"</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="17" t="str">
+      <c r="B34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="19" t="str">
         <f>COUNTIF(D15:D20,"Y")&amp;" of 6"</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="17" t="str">
+      <c r="B35" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="19" t="str">
         <f>COUNTIF(D22:D26,"Y")&amp;" of 5"</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="17" t="str">
+      <c r="B36" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="19" t="str">
         <f>COUNTIF(D28:D31,"Y")&amp;" of 4"</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="19" t="str">
+      <c r="B37" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21" t="str">
         <f>COUNTIF(D5:D31,"Y")&amp;" of 24 met, "&amp;(COUNTIF(D5:D31,"N")+COUNTIF(D5:D31,"?"))&amp;" open"</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
+      <c r="B39" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23" t="str">
         <f>IF(COUNTIF(D5:D13,"Y")=9,IF(COUNTIF(D15:D20,"Y")&gt;=5,"LIKELY ELIGIBLE — Self-certify on SAM.gov","REVIEW CONTROL TESTS — 5+ of 6 should be Y before certifying"),"GAPS IN CORE REQUIREMENTS — Do not self-certify yet")</f>
         <v/>
       </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
     </row>
     <row r="40" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21" t="str">
+      <c r="B40" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="23" t="str">
         <f>IF(COUNTIF(D22:D26,"Y")=5,IF(COUNTIF(D5:D13,"Y")=9,"LIKELY ELIGIBLE for EDWOSB","Confirm WOSB core first"),"EDWOSB GAPS — Check Net Worth tab for exact numbers")</f>
         <v/>
       </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3036,19 +3155,19 @@
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D10:D13">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D15:D20">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D22:D26">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D28:D31">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y, N, or ?" error="Pick Y (met), N (not met), or ? (unsure)" sqref="D5:D13">
-      <formula1>"Y,N,?"</formula1>
+      <formula1>YesNoMaybe</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3060,7 +3179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3077,378 +3196,378 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="E3" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="18"/>
+      <c r="B3" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="E3" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="23">
+      <c r="B4" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="25">
         <v>0</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="23">
+      <c r="E4" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="23">
+      <c r="B5" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="25">
         <v>0</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="23">
+      <c r="E5" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="23">
+      <c r="B6" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="23">
+      <c r="E6" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="25">
         <v>0</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F7" s="25">
+      <c r="E7" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="27">
         <f>AVERAGE(F4:F6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="23">
+      <c r="B8" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="26" t="str">
+      <c r="E8" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F8" s="28" t="str">
         <f>IF(F7&lt;400000,"PASS","FAIL — over $400K")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="23">
+      <c r="B9" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="23">
+      <c r="B10" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="25">
         <v>0</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="18"/>
+      <c r="E10" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="23">
+      <c r="B11" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="25">
         <v>0</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11" s="27">
+      <c r="E11" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="29">
         <f>C15</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="23">
+      <c r="B12" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="26" t="str">
+      <c r="E12" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="28" t="str">
         <f>IF(F11&lt;6500000,"PASS","FAIL — over $6.5M")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="23">
+      <c r="B13" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="23">
+      <c r="B14" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="27">
         <f>SUM(C4:C14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" s="18"/>
+      <c r="E15" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" ht="36" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E16" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="29" t="str">
+      <c r="E16" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="31" t="str">
         <f>IF(AND(C33&lt;850000,F7&lt;400000,F11&lt;6500000),"PASS all 3 thresholds","FAIL — see thresholds above")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="18"/>
+      <c r="B17" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="20"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="23">
+      <c r="B18" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="23">
+      <c r="B19" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="23">
+      <c r="B20" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C21" s="23">
+      <c r="B21" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="23">
+      <c r="B22" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="23">
+      <c r="B23" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="23">
+      <c r="B24" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="23">
+      <c r="B25" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="25">
+      <c r="B26" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="27">
         <f>SUM(C18:C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="18"/>
+      <c r="B28" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="20"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="27">
+      <c r="B29" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="29">
         <f>C15</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="27">
+      <c r="B30" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="29">
         <f>MAX(0,C8-C18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="27">
+      <c r="B31" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="29">
         <f>C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="27">
+      <c r="B32" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="29">
         <f>C26</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="25">
+      <c r="B33" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="27">
         <f>C15-MAX(0,C8-C18)-C11-C26</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="26" t="str">
+      <c r="B34" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="28" t="str">
         <f>IF(C33&lt;850000,"PASS","FAIL — over $850K")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
+      <c r="B36" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
+      <c r="B37" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
     </row>
     <row r="38" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
+      <c r="B38" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
+      <c r="B39" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
     </row>
     <row r="40" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
+      <c r="B40" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3508,7 +3627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3525,606 +3644,606 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>2</v>
+      <c r="C6" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
+      <c r="B7" s="13">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>2</v>
+      <c r="C7" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+      <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>2</v>
+      <c r="C8" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+      <c r="B9" s="13">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>2</v>
+      <c r="C9" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="B10" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+      <c r="B11" s="13">
         <v>6</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>2</v>
+      <c r="C11" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="B12" s="13">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>2</v>
+      <c r="C12" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="11">
+      <c r="B13" s="13">
         <v>8</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>2</v>
+      <c r="C13" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="11">
+      <c r="B15" s="13">
         <v>9</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>2</v>
+      <c r="C15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
+      <c r="B16" s="13">
         <v>10</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="34" t="s">
+      <c r="C16" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E16" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>2</v>
+      <c r="F16" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11">
+      <c r="B17" s="13">
         <v>11</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="34" t="s">
+      <c r="C17" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>2</v>
+      <c r="F17" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="11">
+      <c r="B18" s="13">
         <v>12</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>2</v>
+      <c r="C18" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="11">
+      <c r="B19" s="13">
         <v>13</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="34" t="s">
+      <c r="C19" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>2</v>
+      <c r="F19" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="B20" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="11">
+      <c r="B21" s="13">
         <v>14</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>2</v>
+      <c r="C21" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="11">
-        <v>15</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>2</v>
+      <c r="B22" s="13">
+        <v>15</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="11">
+      <c r="B23" s="13">
         <v>16</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>2</v>
+      <c r="C23" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="11">
+      <c r="B24" s="13">
         <v>17</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>2</v>
+      <c r="C24" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="B25" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="11">
+      <c r="B26" s="13">
         <v>18</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>2</v>
+      <c r="C26" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="11">
+      <c r="B27" s="13">
         <v>19</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>2</v>
+      <c r="C27" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="11">
+      <c r="B28" s="13">
         <v>20</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="34" t="s">
+      <c r="C28" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>2</v>
+      <c r="F28" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="11">
+      <c r="B29" s="13">
         <v>21</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>2</v>
+      <c r="C29" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
+      <c r="B30" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
     </row>
     <row r="31" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <v>22</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>2</v>
+      <c r="C31" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="11">
+      <c r="B32" s="13">
         <v>23</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>2</v>
+      <c r="C32" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="35" t="str">
+      <c r="B34" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="37" t="str">
         <f>COUNTIF(F5:F32,"Have")&amp;" of 23"</f>
         <v/>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="37"/>
     </row>
     <row r="35" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="35" t="str">
+      <c r="B35" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="37" t="str">
         <f>COUNTIF(F5:F32,"Need")&amp;" missing"</f>
         <v/>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="37"/>
     </row>
     <row r="36" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="21" t="str">
+      <c r="B36" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="23" t="str">
         <f>ROUND(COUNTIF(F5:F32,"Have")/23*100,0)&amp;"%"</f>
         <v/>
       </c>
-      <c r="G36" s="21"/>
+      <c r="G36" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4156,22 +4275,22 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F11:F13">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F15:F19">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F21:F24">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F26:F29">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F31:F32">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose status" error="Pick Have, Need, or N/A" sqref="F5:F9">
-      <formula1>"Have,Need,N/A"</formula1>
+      <formula1>DocStatus</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4183,7 +4302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4199,243 +4318,243 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>211</v>
+      <c r="A3" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>214</v>
+      <c r="B4" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>217</v>
+      <c r="B5" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>220</v>
+      <c r="B6" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>223</v>
+      <c r="B7" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>226</v>
+      <c r="B8" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>229</v>
+      <c r="B9" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>232</v>
+      <c r="B10" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>235</v>
+      <c r="B11" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>238</v>
+      <c r="B12" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>241</v>
+      <c r="B13" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>244</v>
+      <c r="B14" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>247</v>
+      <c r="B15" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>250</v>
+      <c r="B16" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>253</v>
+      <c r="B17" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>256</v>
+      <c r="B18" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>259</v>
+      <c r="B19" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>262</v>
+      <c r="B20" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>265</v>
+      <c r="B21" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="23" ht="80" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
+      <c r="B23" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4452,7 +4571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4468,267 +4587,267 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="B3" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="19" t="str">
+      <c r="B4" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="21" t="str">
         <f>IF(BusinessName="","(enter in Business Profile)",BusinessName)</f>
         <v/>
       </c>
-      <c r="D4" s="42" t="s">
-        <v>271</v>
+      <c r="D4" s="44" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="19" t="str">
+      <c r="B5" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="21" t="str">
         <f>IF(PrimaryNAICS="","(enter in Business Profile)",PrimaryNAICS)</f>
         <v/>
       </c>
-      <c r="D5" s="42" t="s">
-        <v>273</v>
+      <c r="D5" s="44" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="19" t="str">
+      <c r="B6" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="21" t="str">
         <f>IF(FemaleOwnerPct="","(enter)",FemaleOwnerPct&amp;"%")</f>
         <v/>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>275</v>
+      <c r="D6" s="44" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
+      <c r="B8" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C9" s="19" t="str">
+      <c r="B9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="21" t="str">
         <f>COUNTIF(WOSBCore,"Y")&amp;" / 9"</f>
         <v/>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>278</v>
+      <c r="D9" s="44" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="C10" s="19" t="str">
+      <c r="B10" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="21" t="str">
         <f>COUNTIF(WOSBControl,"Y")&amp;" / 6"</f>
         <v/>
       </c>
-      <c r="D10" s="42" t="s">
-        <v>280</v>
+      <c r="D10" s="44" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="19" t="str">
+      <c r="B11" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="21" t="str">
         <f>COUNTIF(EDWOSBTests,"Y")&amp;" / 5"</f>
         <v/>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>282</v>
+      <c r="D11" s="44" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="19" t="str">
+      <c r="B12" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="21" t="str">
         <f>COUNTIF(WOSBDocs,"Y")&amp;" / 4"</f>
         <v/>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>284</v>
+      <c r="D12" s="44" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C13" s="19" t="str">
+      <c r="B13" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="21" t="str">
         <f>COUNTIF(DocStatus,"Have")&amp;" of "&amp;COUNTA(DocStatus)</f>
         <v/>
       </c>
-      <c r="D13" s="42" t="s">
-        <v>286</v>
+      <c r="D13" s="44" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
+      <c r="B15" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
     </row>
     <row r="16" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="19" t="str">
+      <c r="B16" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!C33&lt;850000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!C33,"#,##0")&amp;" / $850K)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!C33,"#,##0")&amp;" / $850K)")</f>
         <v/>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>289</v>
+      <c r="D16" s="44" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C17" s="19" t="str">
+      <c r="B17" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!F7&lt;400000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!F7,"#,##0")&amp;" avg)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!F7,"#,##0")&amp;" avg)")</f>
         <v/>
       </c>
-      <c r="D17" s="42" t="s">
-        <v>291</v>
+      <c r="D17" s="44" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C18" s="19" t="str">
+      <c r="B18" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="21" t="str">
         <f>IF('EDWOSB Net Worth'!C15&lt;6500000,"PASS  ($"&amp;TEXT('EDWOSB Net Worth'!C15,"#,##0")&amp;" / $6.5M)","FAIL  ($"&amp;TEXT('EDWOSB Net Worth'!C15,"#,##0")&amp;" / $6.5M)")</f>
         <v/>
       </c>
-      <c r="D18" s="42" t="s">
-        <v>293</v>
+      <c r="D18" s="44" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
+      <c r="B20" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
     </row>
     <row r="21" ht="40" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
-        <v>295</v>
-      </c>
-      <c r="C21" s="29" t="str">
+      <c r="B21" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21" s="31" t="str">
         <f>IF(AND(COUNTIF(WOSBCore,"Y")=9,COUNTIF(WOSBControl,"Y")&gt;=5),"READY — Go update SAM.gov reps &amp; certs","NOT READY — Resolve gaps in WOSB Eligibility tab first")</f>
         <v/>
       </c>
-      <c r="D21" s="29"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" ht="40" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="43" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="29" t="str">
+      <c r="B22" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" s="31" t="str">
         <f>IF(AND(COUNTIF(WOSBCore,"Y")=9,COUNTIF(EDWOSBTests,"Y")=5,'EDWOSB Net Worth'!C33&lt;850000,'EDWOSB Net Worth'!F7&lt;400000,'EDWOSB Net Worth'!C15&lt;6500000),"READY — Self-certify EDWOSB on SAM.gov","NOT READY — Check Net Worth tab + EDWOSB section above")</f>
         <v/>
       </c>
-      <c r="D22" s="29"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
+      <c r="B24" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
     </row>
     <row r="25" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
+      <c r="B25" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
     </row>
     <row r="26" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
+      <c r="B26" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
     </row>
     <row r="27" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
+      <c r="B27" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
     </row>
     <row r="28" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
+      <c r="B28" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
     </row>
     <row r="29" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
+      <c r="B29" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
     </row>
     <row r="30" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
+      <c r="B30" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
     </row>
     <row r="31" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
+      <c r="B31" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
     </row>
     <row r="32" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
+      <c r="B32" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="17">
